--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="21" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{327A2631-75D8-464A-A229-A182B6F7C9EB}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D3AF6BC-0C0E-4360-9369-38ED0841EAAA}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="12432" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="350">
   <si>
     <t>an</t>
   </si>
@@ -1043,6 +1043,39 @@
   </si>
   <si>
     <t>我们的笔</t>
+  </si>
+  <si>
+    <t>《日月明》</t>
+  </si>
+  <si>
+    <t>一人不成众</t>
+  </si>
+  <si>
+    <t>众人一条心</t>
+  </si>
+  <si>
+    <t>日月明</t>
+  </si>
+  <si>
+    <t>田力男</t>
+  </si>
+  <si>
+    <t>二人从</t>
+  </si>
+  <si>
+    <t>三人众</t>
+  </si>
+  <si>
+    <t>双木林</t>
+  </si>
+  <si>
+    <t>三木森</t>
+  </si>
+  <si>
+    <t>黄土变成金</t>
+  </si>
+  <si>
+    <t>我有很多宝贝</t>
   </si>
 </sst>
 </file>
@@ -1398,16 +1431,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F104"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.5234375" customWidth="1"/>
+    <col min="1" max="1" width="12.53125" customWidth="1"/>
     <col min="2" max="2" width="13" customWidth="1"/>
-    <col min="3" max="3" width="16.83984375" customWidth="1"/>
-    <col min="4" max="4" width="21.1015625" customWidth="1"/>
-    <col min="5" max="5" width="18.1015625" customWidth="1"/>
+    <col min="3" max="3" width="16.86328125" customWidth="1"/>
+    <col min="4" max="4" width="21.06640625" customWidth="1"/>
+    <col min="5" max="5" width="18.06640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1427,7 +1460,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1447,7 +1480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -1467,7 +1500,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1487,7 +1520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>39</v>
       </c>
@@ -1507,7 +1540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -1527,7 +1560,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>45</v>
       </c>
@@ -1547,7 +1580,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -1567,7 +1600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -1587,7 +1620,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>54</v>
       </c>
@@ -1607,7 +1640,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -1627,7 +1660,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>60</v>
       </c>
@@ -1647,7 +1680,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -1667,7 +1700,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -1687,7 +1720,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>69</v>
       </c>
@@ -1707,7 +1740,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>71</v>
       </c>
@@ -1727,7 +1760,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>208</v>
       </c>
@@ -1741,7 +1774,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>208</v>
       </c>
@@ -1758,7 +1791,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>74</v>
       </c>
@@ -1772,7 +1805,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>77</v>
       </c>
@@ -1786,7 +1819,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>80</v>
       </c>
@@ -1800,7 +1833,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>85</v>
       </c>
@@ -1814,7 +1847,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>86</v>
       </c>
@@ -1828,7 +1861,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>89</v>
       </c>
@@ -1842,7 +1875,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>92</v>
       </c>
@@ -1856,7 +1889,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>48</v>
       </c>
@@ -1870,7 +1903,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -1884,7 +1917,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>97</v>
       </c>
@@ -1898,7 +1931,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>52</v>
       </c>
@@ -1912,7 +1945,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>102</v>
       </c>
@@ -1926,7 +1959,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>104</v>
       </c>
@@ -1940,7 +1973,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>107</v>
       </c>
@@ -1954,7 +1987,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>110</v>
       </c>
@@ -1968,7 +2001,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>209</v>
       </c>
@@ -1982,7 +2015,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>209</v>
       </c>
@@ -1996,7 +2029,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>113</v>
       </c>
@@ -2010,7 +2043,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>116</v>
       </c>
@@ -2024,7 +2057,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>119</v>
       </c>
@@ -2038,7 +2071,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>122</v>
       </c>
@@ -2052,7 +2085,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>125</v>
       </c>
@@ -2066,7 +2099,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>128</v>
       </c>
@@ -2080,7 +2113,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>107</v>
       </c>
@@ -2094,7 +2127,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>86</v>
       </c>
@@ -2108,7 +2141,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>89</v>
       </c>
@@ -2122,7 +2155,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>83</v>
       </c>
@@ -2136,7 +2169,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>136</v>
       </c>
@@ -2150,7 +2183,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>80</v>
       </c>
@@ -2164,7 +2197,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>97</v>
       </c>
@@ -2178,7 +2211,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>54</v>
       </c>
@@ -2192,7 +2225,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -2206,7 +2239,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>85</v>
       </c>
@@ -2220,7 +2253,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>145</v>
       </c>
@@ -2234,7 +2267,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>163</v>
       </c>
@@ -2248,7 +2281,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>163</v>
       </c>
@@ -2265,7 +2298,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>160</v>
       </c>
@@ -2279,7 +2312,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>164</v>
       </c>
@@ -2293,7 +2326,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>167</v>
       </c>
@@ -2307,7 +2340,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>170</v>
       </c>
@@ -2321,7 +2354,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>173</v>
       </c>
@@ -2335,7 +2368,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
         <v>176</v>
       </c>
@@ -2349,7 +2382,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>179</v>
       </c>
@@ -2363,7 +2396,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>182</v>
       </c>
@@ -2377,7 +2410,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>185</v>
       </c>
@@ -2391,7 +2424,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.55000000000000004">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>113</v>
       </c>
@@ -2405,7 +2438,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>119</v>
       </c>
@@ -2419,7 +2452,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>190</v>
       </c>
@@ -2433,7 +2466,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>193</v>
       </c>
@@ -2447,7 +2480,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>196</v>
       </c>
@@ -2461,7 +2494,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>199</v>
       </c>
@@ -2475,7 +2508,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>80</v>
       </c>
@@ -2489,7 +2522,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>202</v>
       </c>
@@ -2503,7 +2536,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>205</v>
       </c>
@@ -2517,7 +2550,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>210</v>
       </c>
@@ -2531,7 +2564,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>211</v>
       </c>
@@ -2545,7 +2578,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>214</v>
       </c>
@@ -2559,7 +2592,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>217</v>
       </c>
@@ -2573,7 +2606,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>190</v>
       </c>
@@ -2587,7 +2620,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>221</v>
       </c>
@@ -2601,7 +2634,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>224</v>
       </c>
@@ -2615,7 +2648,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>227</v>
       </c>
@@ -2629,7 +2662,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>160</v>
       </c>
@@ -2643,7 +2676,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>164</v>
       </c>
@@ -2657,7 +2690,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>232</v>
       </c>
@@ -2671,7 +2704,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>170</v>
       </c>
@@ -2685,7 +2718,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>173</v>
       </c>
@@ -2699,7 +2732,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>182</v>
       </c>
@@ -2713,7 +2746,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>74</v>
       </c>
@@ -2727,7 +2760,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>199</v>
       </c>
@@ -2741,7 +2774,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>245</v>
       </c>
@@ -2755,7 +2788,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>246</v>
       </c>
@@ -2769,7 +2802,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>249</v>
       </c>
@@ -2783,7 +2816,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>252</v>
       </c>
@@ -2797,7 +2830,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>255</v>
       </c>
@@ -2811,7 +2844,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>258</v>
       </c>
@@ -2825,7 +2858,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>211</v>
       </c>
@@ -2839,7 +2872,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>261</v>
       </c>
@@ -2853,7 +2886,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>264</v>
       </c>
@@ -2867,7 +2900,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>267</v>
       </c>
@@ -2881,7 +2914,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>270</v>
       </c>
@@ -2895,7 +2928,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>273</v>
       </c>
@@ -2909,7 +2942,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>276</v>
       </c>
@@ -2923,7 +2956,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>170</v>
       </c>
@@ -2937,7 +2970,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>232</v>
       </c>
@@ -2951,7 +2984,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>164</v>
       </c>
@@ -2972,16 +3005,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
-  <dimension ref="A1:D62"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:D68"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="16.1015625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.7890625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="13.47265625" style="4" customWidth="1"/>
-    <col min="4" max="4" width="16.5234375" customWidth="1"/>
+    <col min="1" max="1" width="16.06640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.796875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="13.46484375" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16.53125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:4" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -2992,7 +3025,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -3003,7 +3036,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>9</v>
       </c>
@@ -3014,7 +3047,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
@@ -3025,7 +3058,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>11</v>
       </c>
@@ -3036,7 +3069,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="3" t="s">
         <v>17</v>
       </c>
@@ -3045,27 +3078,27 @@
       </c>
       <c r="C6" s="3"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B7" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -3076,7 +3109,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -3084,7 +3117,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -3092,7 +3125,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -3100,7 +3133,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -3108,7 +3141,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -3116,13 +3149,13 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>32</v>
       </c>
       <c r="B17"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" s="4" t="s">
         <v>152</v>
       </c>
@@ -3130,7 +3163,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" s="4" t="s">
         <v>153</v>
       </c>
@@ -3138,7 +3171,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" s="4" t="s">
         <v>154</v>
       </c>
@@ -3146,7 +3179,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" s="4" t="s">
         <v>151</v>
       </c>
@@ -3154,7 +3187,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" s="4" t="s">
         <v>148</v>
       </c>
@@ -3162,7 +3195,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" s="4" t="s">
         <v>157</v>
       </c>
@@ -3170,7 +3203,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" s="4" t="s">
         <v>244</v>
       </c>
@@ -3181,7 +3214,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" s="4" t="s">
         <v>236</v>
       </c>
@@ -3189,7 +3222,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" s="4" t="s">
         <v>237</v>
       </c>
@@ -3197,7 +3230,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" s="4" t="s">
         <v>238</v>
       </c>
@@ -3205,7 +3238,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" s="4" t="s">
         <v>239</v>
       </c>
@@ -3213,7 +3246,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" s="4" t="s">
         <v>281</v>
       </c>
@@ -3224,7 +3257,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" s="4" t="s">
         <v>282</v>
       </c>
@@ -3232,7 +3265,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36" s="4" t="s">
         <v>283</v>
       </c>
@@ -3240,7 +3273,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37" s="4" t="s">
         <v>284</v>
       </c>
@@ -3248,7 +3281,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38" s="4" t="s">
         <v>285</v>
       </c>
@@ -3256,7 +3289,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40" s="4" t="s">
         <v>292</v>
       </c>
@@ -3267,7 +3300,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41" s="4" t="s">
         <v>293</v>
       </c>
@@ -3275,7 +3308,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42" s="4" t="s">
         <v>294</v>
       </c>
@@ -3283,7 +3316,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43" s="4" t="s">
         <v>295</v>
       </c>
@@ -3291,7 +3324,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44" s="4" t="s">
         <v>296</v>
       </c>
@@ -3299,7 +3332,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A46" s="4" t="s">
         <v>303</v>
       </c>
@@ -3313,7 +3346,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A47" s="4" t="s">
         <v>304</v>
       </c>
@@ -3324,7 +3357,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A48" s="4" t="s">
         <v>306</v>
       </c>
@@ -3335,7 +3368,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A49" s="4" t="s">
         <v>305</v>
       </c>
@@ -3346,7 +3379,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A50" s="4" t="s">
         <v>307</v>
       </c>
@@ -3357,7 +3390,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A52" s="4" t="s">
         <v>317</v>
       </c>
@@ -3368,7 +3401,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A53" s="4" t="s">
         <v>320</v>
       </c>
@@ -3376,7 +3409,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A54" s="4" t="s">
         <v>322</v>
       </c>
@@ -3384,7 +3417,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A55" s="4" t="s">
         <v>324</v>
       </c>
@@ -3392,7 +3425,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A56" s="4" t="s">
         <v>326</v>
       </c>
@@ -3400,7 +3433,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A58" s="4" t="s">
         <v>329</v>
       </c>
@@ -3411,7 +3444,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A59" s="4" t="s">
         <v>330</v>
       </c>
@@ -3419,7 +3452,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A60" s="4" t="s">
         <v>331</v>
       </c>
@@ -3427,7 +3460,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A61" s="4" t="s">
         <v>335</v>
       </c>
@@ -3435,12 +3468,55 @@
         <v>333</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A62" s="4" t="s">
         <v>336</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>334</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A64" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="D64" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A65" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A66" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A67" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A68" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>349</v>
       </c>
     </row>
   </sheetData>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D3AF6BC-0C0E-4360-9369-38ED0841EAAA}"/>
+  <xr:revisionPtr revIDLastSave="114" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{237CB095-C280-4E96-92C6-8C3F8C3CE7F8}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="396">
   <si>
     <t>an</t>
   </si>
@@ -1076,6 +1076,144 @@
   </si>
   <si>
     <t>我有很多宝贝</t>
+  </si>
+  <si>
+    <t>《复习一》</t>
+  </si>
+  <si>
+    <t>苹果</t>
+  </si>
+  <si>
+    <t>平果</t>
+  </si>
+  <si>
+    <t>苹棵</t>
+  </si>
+  <si>
+    <t>书包</t>
+  </si>
+  <si>
+    <t>书炮</t>
+  </si>
+  <si>
+    <t>书抱</t>
+  </si>
+  <si>
+    <t>黄金</t>
+  </si>
+  <si>
+    <t>黄全</t>
+  </si>
+  <si>
+    <t>果金</t>
+  </si>
+  <si>
+    <t>太小多少</t>
+  </si>
+  <si>
+    <t>大小多小</t>
+  </si>
+  <si>
+    <t>牛刀</t>
+  </si>
+  <si>
+    <t>午刀</t>
+  </si>
+  <si>
+    <t>牛力</t>
+  </si>
+  <si>
+    <t>真心</t>
+  </si>
+  <si>
+    <t>具心</t>
+  </si>
+  <si>
+    <t>真必</t>
+  </si>
+  <si>
+    <t>本子</t>
+  </si>
+  <si>
+    <t>木子</t>
+  </si>
+  <si>
+    <t>本了</t>
+  </si>
+  <si>
+    <t>笔尖</t>
+  </si>
+  <si>
+    <t>笔尘</t>
+  </si>
+  <si>
+    <t>毛尖</t>
+  </si>
+  <si>
+    <t>明白</t>
+  </si>
+  <si>
+    <t>明自</t>
+  </si>
+  <si>
+    <t>明日</t>
+  </si>
+  <si>
+    <t>田园</t>
+  </si>
+  <si>
+    <t>田口</t>
+  </si>
+  <si>
+    <t>果园</t>
+  </si>
+  <si>
+    <t>土也</t>
+  </si>
+  <si>
+    <t>尘土</t>
+  </si>
+  <si>
+    <t>尘士</t>
+  </si>
+  <si>
+    <t>尖土</t>
+  </si>
+  <si>
+    <t>从小</t>
+  </si>
+  <si>
+    <t>众小</t>
+  </si>
+  <si>
+    <t>从少</t>
+  </si>
+  <si>
+    <t>大众</t>
+  </si>
+  <si>
+    <t>天众</t>
+  </si>
+  <si>
+    <t>犬众</t>
+  </si>
+  <si>
+    <t>林森</t>
+  </si>
+  <si>
+    <t>森木</t>
+  </si>
+  <si>
+    <t>双手</t>
+  </si>
+  <si>
+    <t>又手</t>
+  </si>
+  <si>
+    <t>双毛</t>
+  </si>
+  <si>
+    <t>何水</t>
   </si>
 </sst>
 </file>
@@ -1430,7 +1568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.53125" customWidth="1"/>
@@ -2996,6 +3134,263 @@
       </c>
       <c r="D104" t="s">
         <v>166</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>351</v>
+      </c>
+      <c r="B106" t="s">
+        <v>352</v>
+      </c>
+      <c r="C106" t="s">
+        <v>353</v>
+      </c>
+      <c r="D106" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>354</v>
+      </c>
+      <c r="B107" t="s">
+        <v>354</v>
+      </c>
+      <c r="C107" t="s">
+        <v>355</v>
+      </c>
+      <c r="D107" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>357</v>
+      </c>
+      <c r="B108" t="s">
+        <v>358</v>
+      </c>
+      <c r="C108" t="s">
+        <v>357</v>
+      </c>
+      <c r="D108" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>317</v>
+      </c>
+      <c r="B109" t="s">
+        <v>360</v>
+      </c>
+      <c r="C109" t="s">
+        <v>361</v>
+      </c>
+      <c r="D109" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>362</v>
+      </c>
+      <c r="B110" t="s">
+        <v>362</v>
+      </c>
+      <c r="C110" t="s">
+        <v>363</v>
+      </c>
+      <c r="D110" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A111" t="s">
+        <v>365</v>
+      </c>
+      <c r="B111" t="s">
+        <v>366</v>
+      </c>
+      <c r="C111" t="s">
+        <v>367</v>
+      </c>
+      <c r="D111" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A112" t="s">
+        <v>368</v>
+      </c>
+      <c r="B112" t="s">
+        <v>369</v>
+      </c>
+      <c r="C112" t="s">
+        <v>368</v>
+      </c>
+      <c r="D112" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A113" t="s">
+        <v>371</v>
+      </c>
+      <c r="B113" t="s">
+        <v>371</v>
+      </c>
+      <c r="C113" t="s">
+        <v>372</v>
+      </c>
+      <c r="D113" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A114" t="s">
+        <v>374</v>
+      </c>
+      <c r="B114" t="s">
+        <v>375</v>
+      </c>
+      <c r="C114" t="s">
+        <v>374</v>
+      </c>
+      <c r="D114" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>377</v>
+      </c>
+      <c r="B115" t="s">
+        <v>377</v>
+      </c>
+      <c r="C115" t="s">
+        <v>378</v>
+      </c>
+      <c r="D115" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A116" t="s">
+        <v>249</v>
+      </c>
+      <c r="B116" t="s">
+        <v>250</v>
+      </c>
+      <c r="C116" t="s">
+        <v>380</v>
+      </c>
+      <c r="D116" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A117" t="s">
+        <v>381</v>
+      </c>
+      <c r="B117" t="s">
+        <v>381</v>
+      </c>
+      <c r="C117" t="s">
+        <v>382</v>
+      </c>
+      <c r="D117" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A118" t="s">
+        <v>384</v>
+      </c>
+      <c r="B118" t="s">
+        <v>384</v>
+      </c>
+      <c r="C118" t="s">
+        <v>385</v>
+      </c>
+      <c r="D118" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A119" t="s">
+        <v>387</v>
+      </c>
+      <c r="B119" t="s">
+        <v>388</v>
+      </c>
+      <c r="C119" t="s">
+        <v>389</v>
+      </c>
+      <c r="D119" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A120" t="s">
+        <v>53</v>
+      </c>
+      <c r="B120" t="s">
+        <v>390</v>
+      </c>
+      <c r="C120" t="s">
+        <v>53</v>
+      </c>
+      <c r="D120" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A121" t="s">
+        <v>392</v>
+      </c>
+      <c r="B121" t="s">
+        <v>392</v>
+      </c>
+      <c r="C121" t="s">
+        <v>393</v>
+      </c>
+      <c r="D121" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A122" t="s">
+        <v>170</v>
+      </c>
+      <c r="B122" t="s">
+        <v>172</v>
+      </c>
+      <c r="C122" t="s">
+        <v>170</v>
+      </c>
+      <c r="D122" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A123" t="s">
+        <v>173</v>
+      </c>
+      <c r="B123" t="s">
+        <v>173</v>
+      </c>
+      <c r="C123" t="s">
+        <v>174</v>
+      </c>
+      <c r="D123" t="s">
+        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="114" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{237CB095-C280-4E96-92C6-8C3F8C3CE7F8}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C21548A-B2F5-40D6-89EA-C4EAF717F3E3}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="619" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="409">
   <si>
     <t>an</t>
   </si>
@@ -1214,6 +1214,45 @@
   </si>
   <si>
     <t>何水</t>
+  </si>
+  <si>
+    <t>《大还是小》</t>
+  </si>
+  <si>
+    <t>自己在家</t>
+  </si>
+  <si>
+    <t>到了森林</t>
+  </si>
+  <si>
+    <t>门口有虫子</t>
+  </si>
+  <si>
+    <t>听到爸爸说话</t>
+  </si>
+  <si>
+    <t>下雨打雷</t>
+  </si>
+  <si>
+    <t>不是古人</t>
+  </si>
+  <si>
+    <t>行李多不多</t>
+  </si>
+  <si>
+    <t>白玉在台上</t>
+  </si>
+  <si>
+    <t>时间不多了</t>
+  </si>
+  <si>
+    <t>又有几个</t>
+  </si>
+  <si>
+    <t>比一比大小</t>
+  </si>
+  <si>
+    <t>月儿挂天上</t>
   </si>
 </sst>
 </file>
@@ -3400,7 +3439,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
-  <dimension ref="A1:D68"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.06640625" style="4" bestFit="1" customWidth="1"/>
@@ -3882,7 +3921,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A65" s="4" t="s">
         <v>344</v>
       </c>
@@ -3890,7 +3929,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A66" s="4" t="s">
         <v>340</v>
       </c>
@@ -3898,7 +3937,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A67" s="4" t="s">
         <v>346</v>
       </c>
@@ -3906,12 +3945,63 @@
         <v>347</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A68" s="4" t="s">
         <v>348</v>
       </c>
       <c r="B68" s="4" t="s">
         <v>349</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A70" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>398</v>
+      </c>
+      <c r="D70" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A71" s="4" t="s">
+        <v>399</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A72" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A73" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A74" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A75" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>408</v>
       </c>
     </row>
   </sheetData>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7C21548A-B2F5-40D6-89EA-C4EAF717F3E3}"/>
+  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40179D0F-35A4-41B9-AD8E-D74300296027}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1231,9 +1231,6 @@
     <t>听到爸爸说话</t>
   </si>
   <si>
-    <t>下雨打雷</t>
-  </si>
-  <si>
     <t>不是古人</t>
   </si>
   <si>
@@ -1253,6 +1250,9 @@
   </si>
   <si>
     <t>月儿挂天上</t>
+  </si>
+  <si>
+    <t>雷雨很大</t>
   </si>
 </sst>
 </file>
@@ -3974,34 +3974,34 @@
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A72" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="B72" s="4" t="s">
         <v>401</v>
-      </c>
-      <c r="B72" s="4" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A73" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="B73" s="4" t="s">
         <v>403</v>
-      </c>
-      <c r="B73" s="4" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A74" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="B74" s="4" t="s">
         <v>405</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A75" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>407</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>408</v>
       </c>
     </row>
   </sheetData>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="131" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{40179D0F-35A4-41B9-AD8E-D74300296027}"/>
+  <xr:revisionPtr revIDLastSave="147" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1667B6CA-DF8C-4638-BDB4-AA9D8855BE52}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="420">
   <si>
     <t>an</t>
   </si>
@@ -1253,6 +1253,39 @@
   </si>
   <si>
     <t>雷雨很大</t>
+  </si>
+  <si>
+    <t>《过马路》</t>
+  </si>
+  <si>
+    <t>红灯黄灯</t>
+  </si>
+  <si>
+    <t>小鸟白马</t>
+  </si>
+  <si>
+    <t>要看清</t>
+  </si>
+  <si>
+    <t>自己记下来</t>
+  </si>
+  <si>
+    <t>要走到哪</t>
+  </si>
+  <si>
+    <t>行走在云间</t>
+  </si>
+  <si>
+    <t>记心中</t>
+  </si>
+  <si>
+    <t>有时不好</t>
+  </si>
+  <si>
+    <t>花对树</t>
+  </si>
+  <si>
+    <t>五头牛</t>
   </si>
 </sst>
 </file>
@@ -1338,10 +1371,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3439,7 +3468,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.06640625" style="4" bestFit="1" customWidth="1"/>
@@ -4004,6 +4033,57 @@
         <v>407</v>
       </c>
     </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A77" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="D77" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A78" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A79" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A80" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A81" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A82" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>419</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="147" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1667B6CA-DF8C-4638-BDB4-AA9D8855BE52}"/>
+  <xr:revisionPtr revIDLastSave="200" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F244597B-98D1-4D57-95FE-DCBA97616529}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="645" uniqueCount="420">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="457">
   <si>
     <t>an</t>
   </si>
@@ -1286,6 +1286,117 @@
   </si>
   <si>
     <t>五头牛</t>
+  </si>
+  <si>
+    <t>红灯</t>
+  </si>
+  <si>
+    <t>工灯</t>
+  </si>
+  <si>
+    <t>绿灯</t>
+  </si>
+  <si>
+    <t>飞马</t>
+  </si>
+  <si>
+    <t>行走</t>
+  </si>
+  <si>
+    <t>行李</t>
+  </si>
+  <si>
+    <t>街走</t>
+  </si>
+  <si>
+    <t>看清</t>
+  </si>
+  <si>
+    <t>看青</t>
+  </si>
+  <si>
+    <t>着清</t>
+  </si>
+  <si>
+    <t>不要</t>
+  </si>
+  <si>
+    <t>下要</t>
+  </si>
+  <si>
+    <t>卜要</t>
+  </si>
+  <si>
+    <t>记心间</t>
+  </si>
+  <si>
+    <t>己心间</t>
+  </si>
+  <si>
+    <t>记心问</t>
+  </si>
+  <si>
+    <t>自己</t>
+  </si>
+  <si>
+    <t>白己</t>
+  </si>
+  <si>
+    <t>目己</t>
+  </si>
+  <si>
+    <t>有时</t>
+  </si>
+  <si>
+    <t>看时</t>
+  </si>
+  <si>
+    <t>着时</t>
+  </si>
+  <si>
+    <t>我们</t>
+  </si>
+  <si>
+    <t>我门</t>
+  </si>
+  <si>
+    <t>鹅们</t>
+  </si>
+  <si>
+    <t>门口</t>
+  </si>
+  <si>
+    <t>间口</t>
+  </si>
+  <si>
+    <t>们口</t>
+  </si>
+  <si>
+    <t>听到</t>
+  </si>
+  <si>
+    <t>斤到</t>
+  </si>
+  <si>
+    <t>近到</t>
+  </si>
+  <si>
+    <t>雷雨</t>
+  </si>
+  <si>
+    <t>雪雨</t>
+  </si>
+  <si>
+    <t>雨雷</t>
+  </si>
+  <si>
+    <t>你的</t>
+  </si>
+  <si>
+    <t>尔的</t>
+  </si>
+  <si>
+    <t>你白</t>
   </si>
 </sst>
 </file>
@@ -1371,6 +1482,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1636,7 +1751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.53125" customWidth="1"/>
@@ -3459,6 +3574,193 @@
       </c>
       <c r="D123" t="s">
         <v>395</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A124" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A125" t="s">
+        <v>420</v>
+      </c>
+      <c r="B125" t="s">
+        <v>421</v>
+      </c>
+      <c r="C125" t="s">
+        <v>422</v>
+      </c>
+      <c r="D125" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A126" t="s">
+        <v>423</v>
+      </c>
+      <c r="B126" t="s">
+        <v>423</v>
+      </c>
+      <c r="C126" t="s">
+        <v>190</v>
+      </c>
+      <c r="D126" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A127" t="s">
+        <v>424</v>
+      </c>
+      <c r="B127" t="s">
+        <v>425</v>
+      </c>
+      <c r="C127" t="s">
+        <v>424</v>
+      </c>
+      <c r="D127" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A128" t="s">
+        <v>427</v>
+      </c>
+      <c r="B128" t="s">
+        <v>428</v>
+      </c>
+      <c r="C128" t="s">
+        <v>429</v>
+      </c>
+      <c r="D128" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A129" t="s">
+        <v>430</v>
+      </c>
+      <c r="B129" t="s">
+        <v>431</v>
+      </c>
+      <c r="C129" t="s">
+        <v>430</v>
+      </c>
+      <c r="D129" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A130" t="s">
+        <v>433</v>
+      </c>
+      <c r="B130" t="s">
+        <v>434</v>
+      </c>
+      <c r="C130" t="s">
+        <v>435</v>
+      </c>
+      <c r="D130" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A131" t="s">
+        <v>436</v>
+      </c>
+      <c r="B131" t="s">
+        <v>437</v>
+      </c>
+      <c r="C131" t="s">
+        <v>436</v>
+      </c>
+      <c r="D131" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A132" t="s">
+        <v>439</v>
+      </c>
+      <c r="B132" t="s">
+        <v>439</v>
+      </c>
+      <c r="C132" t="s">
+        <v>440</v>
+      </c>
+      <c r="D132" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A133" t="s">
+        <v>442</v>
+      </c>
+      <c r="B133" t="s">
+        <v>444</v>
+      </c>
+      <c r="C133" t="s">
+        <v>442</v>
+      </c>
+      <c r="D133" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A134" t="s">
+        <v>445</v>
+      </c>
+      <c r="B134" t="s">
+        <v>446</v>
+      </c>
+      <c r="C134" t="s">
+        <v>447</v>
+      </c>
+      <c r="D134" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A135" t="s">
+        <v>448</v>
+      </c>
+      <c r="B135" t="s">
+        <v>449</v>
+      </c>
+      <c r="C135" t="s">
+        <v>448</v>
+      </c>
+      <c r="D135" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A136" t="s">
+        <v>451</v>
+      </c>
+      <c r="B136" t="s">
+        <v>451</v>
+      </c>
+      <c r="C136" t="s">
+        <v>452</v>
+      </c>
+      <c r="D136" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A137" t="s">
+        <v>454</v>
+      </c>
+      <c r="B137" t="s">
+        <v>455</v>
+      </c>
+      <c r="C137" t="s">
+        <v>454</v>
+      </c>
+      <c r="D137" t="s">
+        <v>456</v>
       </c>
     </row>
   </sheetData>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="200" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F244597B-98D1-4D57-95FE-DCBA97616529}"/>
+  <xr:revisionPtr revIDLastSave="214" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54AF4A82-8A50-48EE-AF26-B63FD7CD93C5}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="468">
   <si>
     <t>an</t>
   </si>
@@ -1397,6 +1397,39 @@
   </si>
   <si>
     <t>你白</t>
+  </si>
+  <si>
+    <t>《积少成多》</t>
+  </si>
+  <si>
+    <t>只怕有心人</t>
+  </si>
+  <si>
+    <t>四年不出家门</t>
+  </si>
+  <si>
+    <t>世上无水牛</t>
+  </si>
+  <si>
+    <t>分清红灯黄灯</t>
+  </si>
+  <si>
+    <t>要走到花园</t>
+  </si>
+  <si>
+    <t>妈妈的话记心间</t>
+  </si>
+  <si>
+    <t>马不是鸟</t>
+  </si>
+  <si>
+    <t>自己听一听</t>
+  </si>
+  <si>
+    <t>到果园一看</t>
+  </si>
+  <si>
+    <t>有雷有雨</t>
   </si>
 </sst>
 </file>
@@ -3770,7 +3803,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.06640625" style="4" bestFit="1" customWidth="1"/>
@@ -4370,7 +4403,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A81" s="4" t="s">
         <v>21</v>
       </c>
@@ -4378,12 +4411,55 @@
         <v>418</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A82" s="4" t="s">
         <v>318</v>
       </c>
       <c r="B82" s="4" t="s">
         <v>419</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A84" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="D84" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A85" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A86" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A87" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A88" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>467</v>
       </c>
     </row>
   </sheetData>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="214" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54AF4A82-8A50-48EE-AF26-B63FD7CD93C5}"/>
+  <xr:revisionPtr revIDLastSave="286" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{088AF4AD-EB4E-46A4-B774-B9FCF713D1B1}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="510">
   <si>
     <t>an</t>
   </si>
@@ -1430,6 +1430,132 @@
   </si>
   <si>
     <t>有雷有雨</t>
+  </si>
+  <si>
+    <t>《乌鸦喝水》</t>
+  </si>
+  <si>
+    <t>乌云</t>
+  </si>
+  <si>
+    <t>鸟云</t>
+  </si>
+  <si>
+    <t>马云</t>
+  </si>
+  <si>
+    <t>找一找</t>
+  </si>
+  <si>
+    <t>我一我</t>
+  </si>
+  <si>
+    <t>找一我</t>
+  </si>
+  <si>
+    <t>办法</t>
+  </si>
+  <si>
+    <t>石头</t>
+  </si>
+  <si>
+    <t>右头</t>
+  </si>
+  <si>
+    <t>石犬</t>
+  </si>
+  <si>
+    <t>办不到</t>
+  </si>
+  <si>
+    <t>办云</t>
+  </si>
+  <si>
+    <t>办去</t>
+  </si>
+  <si>
+    <t>力不到</t>
+  </si>
+  <si>
+    <t>为不到</t>
+  </si>
+  <si>
+    <t>七分</t>
+  </si>
+  <si>
+    <t>九分</t>
+  </si>
+  <si>
+    <t>七份</t>
+  </si>
+  <si>
+    <t>去年</t>
+  </si>
+  <si>
+    <t>去季</t>
+  </si>
+  <si>
+    <t>去千</t>
+  </si>
+  <si>
+    <t>世上</t>
+  </si>
+  <si>
+    <t>世下</t>
+  </si>
+  <si>
+    <t>泄上</t>
+  </si>
+  <si>
+    <t>怕人</t>
+  </si>
+  <si>
+    <t>白人</t>
+  </si>
+  <si>
+    <t>柏人</t>
+  </si>
+  <si>
+    <t>台子</t>
+  </si>
+  <si>
+    <t>台了</t>
+  </si>
+  <si>
+    <t>抬子</t>
+  </si>
+  <si>
+    <t>红火</t>
+  </si>
+  <si>
+    <t>红丁</t>
+  </si>
+  <si>
+    <t>不西</t>
+  </si>
+  <si>
+    <t>不女</t>
+  </si>
+  <si>
+    <t>灯走</t>
+  </si>
+  <si>
+    <t>日记</t>
+  </si>
+  <si>
+    <t>目记</t>
+  </si>
+  <si>
+    <t>日己</t>
+  </si>
+  <si>
+    <t>中间</t>
+  </si>
+  <si>
+    <t>中门</t>
+  </si>
+  <si>
+    <t>虫间</t>
   </si>
 </sst>
 </file>
@@ -1784,7 +1910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F137"/>
+  <dimension ref="A1:F154"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="12.53125" customWidth="1"/>
@@ -3794,6 +3920,235 @@
       </c>
       <c r="D137" t="s">
         <v>456</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A138" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A139" t="s">
+        <v>469</v>
+      </c>
+      <c r="B139" t="s">
+        <v>470</v>
+      </c>
+      <c r="C139" t="s">
+        <v>469</v>
+      </c>
+      <c r="D139" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>472</v>
+      </c>
+      <c r="B140" t="s">
+        <v>473</v>
+      </c>
+      <c r="C140" t="s">
+        <v>474</v>
+      </c>
+      <c r="D140" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>475</v>
+      </c>
+      <c r="B141" t="s">
+        <v>475</v>
+      </c>
+      <c r="C141" t="s">
+        <v>480</v>
+      </c>
+      <c r="D141" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A142" t="s">
+        <v>476</v>
+      </c>
+      <c r="B142" t="s">
+        <v>477</v>
+      </c>
+      <c r="C142" t="s">
+        <v>476</v>
+      </c>
+      <c r="D142" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A143" t="s">
+        <v>479</v>
+      </c>
+      <c r="B143" t="s">
+        <v>482</v>
+      </c>
+      <c r="C143" t="s">
+        <v>483</v>
+      </c>
+      <c r="D143" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A144" t="s">
+        <v>484</v>
+      </c>
+      <c r="B144" t="s">
+        <v>484</v>
+      </c>
+      <c r="C144" t="s">
+        <v>485</v>
+      </c>
+      <c r="D144" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A145" t="s">
+        <v>487</v>
+      </c>
+      <c r="B145" t="s">
+        <v>488</v>
+      </c>
+      <c r="C145" t="s">
+        <v>487</v>
+      </c>
+      <c r="D145" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A146" t="s">
+        <v>490</v>
+      </c>
+      <c r="B146" t="s">
+        <v>491</v>
+      </c>
+      <c r="C146" t="s">
+        <v>492</v>
+      </c>
+      <c r="D146" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A147" t="s">
+        <v>493</v>
+      </c>
+      <c r="B147" t="s">
+        <v>494</v>
+      </c>
+      <c r="C147" t="s">
+        <v>493</v>
+      </c>
+      <c r="D147" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A148" t="s">
+        <v>496</v>
+      </c>
+      <c r="B148" t="s">
+        <v>497</v>
+      </c>
+      <c r="C148" t="s">
+        <v>498</v>
+      </c>
+      <c r="D148" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A149" t="s">
+        <v>420</v>
+      </c>
+      <c r="B149" t="s">
+        <v>499</v>
+      </c>
+      <c r="C149" t="s">
+        <v>420</v>
+      </c>
+      <c r="D149" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A150" t="s">
+        <v>430</v>
+      </c>
+      <c r="B150" t="s">
+        <v>430</v>
+      </c>
+      <c r="C150" t="s">
+        <v>501</v>
+      </c>
+      <c r="D150" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A151" t="s">
+        <v>427</v>
+      </c>
+      <c r="B151" t="s">
+        <v>428</v>
+      </c>
+      <c r="C151" t="s">
+        <v>427</v>
+      </c>
+      <c r="D151" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A152" t="s">
+        <v>424</v>
+      </c>
+      <c r="B152" t="s">
+        <v>424</v>
+      </c>
+      <c r="C152" t="s">
+        <v>426</v>
+      </c>
+      <c r="D152" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A153" t="s">
+        <v>504</v>
+      </c>
+      <c r="B153" t="s">
+        <v>505</v>
+      </c>
+      <c r="C153" t="s">
+        <v>506</v>
+      </c>
+      <c r="D153" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A154" t="s">
+        <v>507</v>
+      </c>
+      <c r="B154" t="s">
+        <v>507</v>
+      </c>
+      <c r="C154" t="s">
+        <v>508</v>
+      </c>
+      <c r="D154" t="s">
+        <v>509</v>
       </c>
     </row>
   </sheetData>

--- a/content/table1.xlsx
+++ b/content/table1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1d8c3d380d53cb8/Desktop/工作/xiaowenwenweb/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="286" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{088AF4AD-EB4E-46A4-B774-B9FCF713D1B1}"/>
+  <xr:revisionPtr revIDLastSave="303" documentId="13_ncr:1_{C9A72E67-01CA-49C3-BBD5-A97C83FD83F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30BA3D84-42C5-4ED9-BECB-70A367576DCB}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="774" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="520">
   <si>
     <t>an</t>
   </si>
@@ -1556,6 +1556,36 @@
   </si>
   <si>
     <t>虫间</t>
+  </si>
+  <si>
+    <t>自己走一走</t>
+  </si>
+  <si>
+    <t>要记在心间</t>
+  </si>
+  <si>
+    <t>是不是红灯</t>
+  </si>
+  <si>
+    <t>到家看一看</t>
+  </si>
+  <si>
+    <t>乌鸦有办法</t>
+  </si>
+  <si>
+    <t>门口有什么</t>
+  </si>
+  <si>
+    <t>分清雨雪雷</t>
+  </si>
+  <si>
+    <t>找一找石头</t>
+  </si>
+  <si>
+    <t>明年去找人</t>
+  </si>
+  <si>
+    <t>《复习课二》</t>
   </si>
 </sst>
 </file>
@@ -4158,7 +4188,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75BA1470-2FAC-4638-B711-50B7F8590946}">
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D94"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.06640625" style="4" bestFit="1" customWidth="1"/>
@@ -4817,6 +4847,49 @@
         <v>467</v>
       </c>
     </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A90" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="D90" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A91" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A92" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A93" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A94" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>514</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
